--- a/artfynd/S 2741-2022 artfynd.xlsx
+++ b/artfynd/S 2741-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/278438</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6792829</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7059543</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6792805</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6792833</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7059541</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7059542</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
           <t>Ekoxeuppropet 2020</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98327530</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1621,6 +1666,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6792797</t>
         </is>
       </c>
     </row>
@@ -1738,6 +1788,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079105</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1848,6 +1903,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079896</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1958,6 +2018,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079897</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079898</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2178,6 +2248,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079899</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2288,6 +2363,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079900</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2398,6 +2478,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079901</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2508,6 +2593,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079903</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2618,6 +2708,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079904</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2728,6 +2823,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079905</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2838,6 +2938,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079906</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2948,6 +3053,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103081007</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3058,6 +3168,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103081008</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3288,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103081009</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3283,6 +3403,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103081010</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3393,6 +3518,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103081012</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3503,6 +3633,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103081013</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3613,6 +3748,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103081015</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3721,6 +3861,11 @@
       <c r="AY29" t="inlineStr">
         <is>
           <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103081016</t>
         </is>
       </c>
     </row>
@@ -3838,6 +3983,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103092125</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3953,6 +4103,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103092126</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4063,6 +4218,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178427</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4173,6 +4333,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178428</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4283,6 +4448,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178429</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4393,6 +4563,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178430</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4503,6 +4678,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178431</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4613,6 +4793,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178432</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4723,6 +4908,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178433</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4833,6 +5023,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178434</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4943,6 +5138,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178435</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5053,6 +5253,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178436</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5163,6 +5368,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178437</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5273,6 +5483,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178438</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5383,6 +5598,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178439</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5493,6 +5713,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178440</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5603,6 +5828,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178441</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5713,6 +5943,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178442</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5823,6 +6058,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178444</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5933,6 +6173,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178445</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6043,6 +6288,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178446</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6144,6 +6394,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6792798</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6259,6 +6514,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61074517</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6374,6 +6634,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61074518</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6489,6 +6754,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61074519</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6607,8 +6877,69 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61074520</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>